--- a/Nuevos DeepWins/Problem3_CheckerRotated/Res/Comparativa_15_Neuronas.xlsx
+++ b/Nuevos DeepWins/Problem3_CheckerRotated/Res/Comparativa_15_Neuronas.xlsx
@@ -581,35 +581,43 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.249491</v>
+        <v>0.241971</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E2" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
         <v>200000</v>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0.547085</v>
+      </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>0.478431</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.51046</v>
+      </c>
       <c r="J2" t="n">
-        <v>0.250196</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>0.25889</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.471503</v>
+      </c>
       <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>0.461929</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.466667</v>
+      </c>
       <c r="N2" t="n">
         <v>0.2</v>
       </c>
@@ -644,23 +652,23 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_11.txt</t>
+          <t>_2_15_1_1790731436_19.txt</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z2" t="n">
         <v>15</v>
       </c>
       <c r="AA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -674,43 +682,35 @@
         <v>0.1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.242036</v>
+        <v>0.249519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F3" t="n">
         <v>200000</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.550702</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.461438</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.502134</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>0.25872</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.478947</v>
-      </c>
+        <v>0.25015</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>0.461929</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.470284</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>0.2</v>
       </c>
@@ -745,23 +745,23 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_8.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_19.txt</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z3" t="n">
         <v>15</v>
       </c>
       <c r="AA3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -775,7 +775,7 @@
         <v>0.1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.249523</v>
+        <v>0.24952</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>0.25015</v>
+        <v>0.250147</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
@@ -838,7 +838,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_12.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_2.txt</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -868,35 +868,43 @@
         <v>0.1</v>
       </c>
       <c r="B5" t="n">
-        <v>0.249519</v>
+        <v>0.241913</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E5" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
         <v>200000</v>
       </c>
-      <c r="G5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0.554396</v>
+      </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>0.486275</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.518106</v>
+      </c>
       <c r="J5" t="n">
-        <v>0.250157</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0.259112</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.484536</v>
+      </c>
       <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>0.477157</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.480818</v>
+      </c>
       <c r="N5" t="n">
         <v>0.2</v>
       </c>
@@ -931,23 +939,23 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_3.txt</t>
+          <t>_2_15_1_1790731436_0.txt</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z5" t="n">
         <v>15</v>
       </c>
       <c r="AA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1054,43 +1062,35 @@
         <v>0.1</v>
       </c>
       <c r="B7" t="n">
-        <v>0.242021</v>
+        <v>0.249519</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E7" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F7" t="n">
         <v>200000</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.543575</v>
-      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.481046</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.510402</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>0.258573</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.463918</v>
-      </c>
+        <v>0.250157</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.456853</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.460358</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>0.2</v>
       </c>
@@ -1125,23 +1125,23 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_3.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_3.txt</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z7" t="n">
         <v>15</v>
       </c>
       <c r="AA7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1155,35 +1155,43 @@
         <v>0.1</v>
       </c>
       <c r="B8" t="n">
-        <v>0.24952</v>
+        <v>0.242237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E8" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F8" t="n">
         <v>200000</v>
       </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0.549114</v>
+      </c>
       <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>0.445752</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.492063</v>
+      </c>
       <c r="J8" t="n">
-        <v>0.250147</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
+        <v>0.258884</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.477778</v>
+      </c>
       <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
+        <v>0.436548</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.456233</v>
+      </c>
       <c r="N8" t="n">
         <v>0.2</v>
       </c>
@@ -1218,23 +1226,23 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_2.txt</t>
+          <t>_2_15_1_1790731436_13.txt</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z8" t="n">
         <v>15</v>
       </c>
       <c r="AA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1248,7 +1256,7 @@
         <v>0.1</v>
       </c>
       <c r="B9" t="n">
-        <v>0.249519</v>
+        <v>0.249526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1270,7 +1278,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>0.25015</v>
+        <v>0.250144</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
@@ -1311,7 +1319,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_19.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_8.txt</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1341,35 +1349,43 @@
         <v>0.1</v>
       </c>
       <c r="B10" t="n">
-        <v>0.249526</v>
+        <v>0.242036</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E10" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F10" t="n">
         <v>200000</v>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="n">
+        <v>0.550702</v>
+      </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0.461438</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.502134</v>
+      </c>
       <c r="J10" t="n">
-        <v>0.250138</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
+        <v>0.25872</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.478947</v>
+      </c>
       <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
+        <v>0.461929</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.470284</v>
+      </c>
       <c r="N10" t="n">
         <v>0.2</v>
       </c>
@@ -1404,23 +1420,23 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_10.txt</t>
+          <t>_2_15_1_1790731436_8.txt</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z10" t="n">
         <v>15</v>
       </c>
       <c r="AA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1434,43 +1450,35 @@
         <v>0.1</v>
       </c>
       <c r="B11" t="n">
-        <v>0.24212</v>
+        <v>0.249522</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E11" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F11" t="n">
         <v>200000</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.535456</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.48366</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.508242</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>0.258393</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.466321</v>
-      </c>
+        <v>0.25015</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>0.456853</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.461538</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>0.2</v>
       </c>
@@ -1505,23 +1513,23 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_10.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_17.txt</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z11" t="n">
         <v>15</v>
       </c>
       <c r="AA11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1535,7 +1543,7 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.242169</v>
+        <v>0.242043</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1552,25 +1560,25 @@
         <v>200000</v>
       </c>
       <c r="G12" t="n">
-        <v>0.548336</v>
+        <v>0.5516180000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.452288</v>
+        <v>0.467974</v>
       </c>
       <c r="I12" t="n">
-        <v>0.495702</v>
+        <v>0.506365</v>
       </c>
       <c r="J12" t="n">
-        <v>0.258467</v>
+        <v>0.258862</v>
       </c>
       <c r="K12" t="n">
-        <v>0.475676</v>
+        <v>0.478947</v>
       </c>
       <c r="L12" t="n">
-        <v>0.446701</v>
+        <v>0.461929</v>
       </c>
       <c r="M12" t="n">
-        <v>0.460733</v>
+        <v>0.470284</v>
       </c>
       <c r="N12" t="n">
         <v>0.2</v>
@@ -1606,7 +1614,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_7.txt</t>
+          <t>_2_15_1_1790731436_2.txt</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1636,7 +1644,7 @@
         <v>0.1</v>
       </c>
       <c r="B13" t="n">
-        <v>0.249505</v>
+        <v>0.249519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1658,7 +1666,7 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>0.250177</v>
+        <v>0.250155</v>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
@@ -1699,7 +1707,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_13.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_1.txt</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -1729,43 +1737,35 @@
         <v>0.1</v>
       </c>
       <c r="B14" t="n">
-        <v>0.24228</v>
+        <v>0.249526</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E14" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F14" t="n">
         <v>200000</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.539171</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.458824</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.495763</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>0.258443</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.466667</v>
-      </c>
+        <v>0.250138</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.461929</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.464286</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>0.2</v>
       </c>
@@ -1800,23 +1800,23 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_18.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_10.txt</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z14" t="n">
         <v>15</v>
       </c>
       <c r="AA14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1830,43 +1830,35 @@
         <v>0.1</v>
       </c>
       <c r="B15" t="n">
-        <v>0.242014</v>
+        <v>0.24952</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E15" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F15" t="n">
         <v>200000</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.55832</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.469281</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.509943</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>0.259005</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.478947</v>
-      </c>
+        <v>0.250149</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>0.461929</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.470284</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0.2</v>
       </c>
@@ -1901,23 +1893,23 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_7.txt</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z15" t="n">
         <v>15</v>
       </c>
       <c r="AA15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1931,7 +1923,7 @@
         <v>0.1</v>
       </c>
       <c r="B16" t="n">
-        <v>0.249522</v>
+        <v>0.249524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1953,7 +1945,7 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
-        <v>0.25015</v>
+        <v>0.250147</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
@@ -1994,7 +1986,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_4.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_6.txt</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2024,7 +2016,7 @@
         <v>0.1</v>
       </c>
       <c r="B17" t="n">
-        <v>0.242389</v>
+        <v>0.242014</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2041,25 +2033,25 @@
         <v>200000</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5552049999999999</v>
+        <v>0.55832</v>
       </c>
       <c r="H17" t="n">
-        <v>0.460131</v>
+        <v>0.469281</v>
       </c>
       <c r="I17" t="n">
-        <v>0.503217</v>
+        <v>0.509943</v>
       </c>
       <c r="J17" t="n">
-        <v>0.258841</v>
+        <v>0.259005</v>
       </c>
       <c r="K17" t="n">
-        <v>0.460733</v>
+        <v>0.478947</v>
       </c>
       <c r="L17" t="n">
-        <v>0.446701</v>
+        <v>0.461929</v>
       </c>
       <c r="M17" t="n">
-        <v>0.453608</v>
+        <v>0.470284</v>
       </c>
       <c r="N17" t="n">
         <v>0.2</v>
@@ -2095,7 +2087,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_6.txt</t>
+          <t>_2_15_1_1790731436_4.txt</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2125,7 +2117,7 @@
         <v>0.1</v>
       </c>
       <c r="B18" t="n">
-        <v>0.241889</v>
+        <v>0.242124</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2142,25 +2134,25 @@
         <v>200000</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.554098</v>
       </c>
       <c r="H18" t="n">
-        <v>0.494118</v>
+        <v>0.44183</v>
       </c>
       <c r="I18" t="n">
-        <v>0.525</v>
+        <v>0.491636</v>
       </c>
       <c r="J18" t="n">
-        <v>0.259042</v>
+        <v>0.258685</v>
       </c>
       <c r="K18" t="n">
-        <v>0.494949</v>
+        <v>0.468927</v>
       </c>
       <c r="L18" t="n">
-        <v>0.497462</v>
+        <v>0.42132</v>
       </c>
       <c r="M18" t="n">
-        <v>0.496203</v>
+        <v>0.44385</v>
       </c>
       <c r="N18" t="n">
         <v>0.2</v>
@@ -2196,7 +2188,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_1.txt</t>
+          <t>_2_15_1_1790731436_9.txt</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2226,43 +2218,35 @@
         <v>0.1</v>
       </c>
       <c r="B19" t="n">
-        <v>0.242279</v>
+        <v>0.249505</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E19" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F19" t="n">
         <v>200000</v>
       </c>
-      <c r="G19" t="n">
-        <v>0.544164</v>
-      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.45098</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0.493209</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>0.258514</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.464865</v>
-      </c>
+        <v>0.250177</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="n">
-        <v>0.436548</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.450262</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>0.2</v>
       </c>
@@ -2297,23 +2281,23 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_11.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_13.txt</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z19" t="n">
         <v>15</v>
       </c>
       <c r="AA19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2327,7 +2311,7 @@
         <v>0.1</v>
       </c>
       <c r="B20" t="n">
-        <v>0.249519</v>
+        <v>0.249522</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2349,7 +2333,7 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>0.250155</v>
+        <v>0.250151</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="n">
@@ -2390,7 +2374,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_9.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_0.txt</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2420,7 +2404,7 @@
         <v>0.1</v>
       </c>
       <c r="B21" t="n">
-        <v>0.242145</v>
+        <v>0.241863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2437,25 +2421,25 @@
         <v>200000</v>
       </c>
       <c r="G21" t="n">
-        <v>0.542243</v>
+        <v>0.549401</v>
       </c>
       <c r="H21" t="n">
-        <v>0.461438</v>
+        <v>0.479739</v>
       </c>
       <c r="I21" t="n">
-        <v>0.498588</v>
+        <v>0.512212</v>
       </c>
       <c r="J21" t="n">
-        <v>0.258167</v>
+        <v>0.25893</v>
       </c>
       <c r="K21" t="n">
-        <v>0.463918</v>
+        <v>0.489899</v>
       </c>
       <c r="L21" t="n">
-        <v>0.456853</v>
+        <v>0.492386</v>
       </c>
       <c r="M21" t="n">
-        <v>0.460358</v>
+        <v>0.491139</v>
       </c>
       <c r="N21" t="n">
         <v>0.2</v>
@@ -2491,7 +2475,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_5.txt</t>
+          <t>_2_15_1_1790731436_15.txt</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2521,43 +2505,35 @@
         <v>0.1</v>
       </c>
       <c r="B22" t="n">
-        <v>0.241971</v>
+        <v>0.249511</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E22" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F22" t="n">
         <v>200000</v>
       </c>
-      <c r="G22" t="n">
-        <v>0.547085</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>0.478431</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.51046</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>0.25889</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.471503</v>
-      </c>
+        <v>0.250165</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="n">
-        <v>0.461929</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.466667</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0.2</v>
       </c>
@@ -2592,23 +2568,23 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_19.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_18.txt</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z22" t="n">
         <v>15</v>
       </c>
       <c r="AA22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -2622,7 +2598,7 @@
         <v>0.1</v>
       </c>
       <c r="B23" t="n">
-        <v>0.242043</v>
+        <v>0.241829</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2639,25 +2615,25 @@
         <v>200000</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5516180000000001</v>
+        <v>0.558346</v>
       </c>
       <c r="H23" t="n">
-        <v>0.467974</v>
+        <v>0.494118</v>
       </c>
       <c r="I23" t="n">
-        <v>0.506365</v>
+        <v>0.524272</v>
       </c>
       <c r="J23" t="n">
-        <v>0.258862</v>
+        <v>0.258833</v>
       </c>
       <c r="K23" t="n">
-        <v>0.478947</v>
+        <v>0.494949</v>
       </c>
       <c r="L23" t="n">
-        <v>0.461929</v>
+        <v>0.497462</v>
       </c>
       <c r="M23" t="n">
-        <v>0.470284</v>
+        <v>0.496203</v>
       </c>
       <c r="N23" t="n">
         <v>0.2</v>
@@ -2693,7 +2669,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_2.txt</t>
+          <t>_2_15_1_1790731436_16.txt</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -2723,7 +2699,7 @@
         <v>0.1</v>
       </c>
       <c r="B24" t="n">
-        <v>0.24952</v>
+        <v>0.249511</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2745,7 +2721,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>0.250149</v>
+        <v>0.250172</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="n">
@@ -2786,7 +2762,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_7.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_14.txt</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -2816,35 +2792,43 @@
         <v>0.1</v>
       </c>
       <c r="B25" t="n">
-        <v>0.249522</v>
+        <v>0.242021</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E25" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F25" t="n">
         <v>200000</v>
       </c>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>0.543575</v>
+      </c>
       <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>0.481046</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.510402</v>
+      </c>
       <c r="J25" t="n">
-        <v>0.25015</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
+        <v>0.258573</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.463918</v>
+      </c>
       <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="inlineStr"/>
+        <v>0.456853</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.460358</v>
+      </c>
       <c r="N25" t="n">
         <v>0.2</v>
       </c>
@@ -2879,23 +2863,23 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_17.txt</t>
+          <t>_2_15_1_1790731436_3.txt</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z25" t="n">
         <v>15</v>
       </c>
       <c r="AA25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -2909,7 +2893,7 @@
         <v>0.1</v>
       </c>
       <c r="B26" t="n">
-        <v>0.249524</v>
+        <v>0.249523</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -2931,7 +2915,7 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>0.250147</v>
+        <v>0.25015</v>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="n">
@@ -2972,7 +2956,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_6.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_12.txt</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -3002,7 +2986,7 @@
         <v>0.1</v>
       </c>
       <c r="B27" t="n">
-        <v>0.241829</v>
+        <v>0.24228</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3019,25 +3003,25 @@
         <v>200000</v>
       </c>
       <c r="G27" t="n">
-        <v>0.558346</v>
+        <v>0.539171</v>
       </c>
       <c r="H27" t="n">
-        <v>0.494118</v>
+        <v>0.458824</v>
       </c>
       <c r="I27" t="n">
-        <v>0.524272</v>
+        <v>0.495763</v>
       </c>
       <c r="J27" t="n">
-        <v>0.258833</v>
+        <v>0.258443</v>
       </c>
       <c r="K27" t="n">
-        <v>0.494949</v>
+        <v>0.466667</v>
       </c>
       <c r="L27" t="n">
-        <v>0.497462</v>
+        <v>0.461929</v>
       </c>
       <c r="M27" t="n">
-        <v>0.496203</v>
+        <v>0.464286</v>
       </c>
       <c r="N27" t="n">
         <v>0.2</v>
@@ -3073,7 +3057,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_16.txt</t>
+          <t>_2_15_1_1790731436_18.txt</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -3204,35 +3188,43 @@
         <v>0.1</v>
       </c>
       <c r="B29" t="n">
-        <v>0.249519</v>
+        <v>0.242145</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E29" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F29" t="n">
         <v>200000</v>
       </c>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>0.542243</v>
+      </c>
       <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>0.461438</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.498588</v>
+      </c>
       <c r="J29" t="n">
-        <v>0.250155</v>
-      </c>
-      <c r="K29" t="inlineStr"/>
+        <v>0.258167</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.463918</v>
+      </c>
       <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr"/>
+        <v>0.456853</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.460358</v>
+      </c>
       <c r="N29" t="n">
         <v>0.2</v>
       </c>
@@ -3267,23 +3259,23 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_1.txt</t>
+          <t>_2_15_1_1790731436_5.txt</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z29" t="n">
         <v>15</v>
       </c>
       <c r="AA29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3297,43 +3289,35 @@
         <v>0.1</v>
       </c>
       <c r="B30" t="n">
-        <v>0.241913</v>
+        <v>0.249519</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E30" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F30" t="n">
         <v>200000</v>
       </c>
-      <c r="G30" t="n">
-        <v>0.554396</v>
-      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>0.486275</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.518106</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>0.259112</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.484536</v>
-      </c>
+        <v>0.250155</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="n">
-        <v>0.477157</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.480818</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>0.2</v>
       </c>
@@ -3368,23 +3352,23 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_0.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_9.txt</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z30" t="n">
         <v>15</v>
       </c>
       <c r="AA30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -3398,7 +3382,7 @@
         <v>0.1</v>
       </c>
       <c r="B31" t="n">
-        <v>0.241885</v>
+        <v>0.241889</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3415,25 +3399,25 @@
         <v>200000</v>
       </c>
       <c r="G31" t="n">
-        <v>0.556426</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.464052</v>
+        <v>0.494118</v>
       </c>
       <c r="I31" t="n">
-        <v>0.506058</v>
+        <v>0.525</v>
       </c>
       <c r="J31" t="n">
-        <v>0.259202</v>
+        <v>0.259042</v>
       </c>
       <c r="K31" t="n">
-        <v>0.484043</v>
+        <v>0.494949</v>
       </c>
       <c r="L31" t="n">
-        <v>0.461929</v>
+        <v>0.497462</v>
       </c>
       <c r="M31" t="n">
-        <v>0.472727</v>
+        <v>0.496203</v>
       </c>
       <c r="N31" t="n">
         <v>0.2</v>
@@ -3469,7 +3453,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_17.txt</t>
+          <t>_2_15_1_1790731436_1.txt</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -3499,35 +3483,43 @@
         <v>0.1</v>
       </c>
       <c r="B32" t="n">
-        <v>0.249526</v>
+        <v>0.242279</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F32" t="n">
         <v>200000</v>
       </c>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>0.544164</v>
+      </c>
       <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>0.45098</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.493209</v>
+      </c>
       <c r="J32" t="n">
-        <v>0.250144</v>
-      </c>
-      <c r="K32" t="inlineStr"/>
+        <v>0.258514</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.464865</v>
+      </c>
       <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr"/>
+        <v>0.436548</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.450262</v>
+      </c>
       <c r="N32" t="n">
         <v>0.2</v>
       </c>
@@ -3562,23 +3554,23 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_8.txt</t>
+          <t>_2_15_1_1790731436_11.txt</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z32" t="n">
         <v>15</v>
       </c>
       <c r="AA32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -3685,7 +3677,7 @@
         <v>0.1</v>
       </c>
       <c r="B34" t="n">
-        <v>0.241863</v>
+        <v>0.242389</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3702,25 +3694,25 @@
         <v>200000</v>
       </c>
       <c r="G34" t="n">
-        <v>0.549401</v>
+        <v>0.5552049999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>0.479739</v>
+        <v>0.460131</v>
       </c>
       <c r="I34" t="n">
-        <v>0.512212</v>
+        <v>0.503217</v>
       </c>
       <c r="J34" t="n">
-        <v>0.25893</v>
+        <v>0.258841</v>
       </c>
       <c r="K34" t="n">
-        <v>0.489899</v>
+        <v>0.460733</v>
       </c>
       <c r="L34" t="n">
-        <v>0.492386</v>
+        <v>0.446701</v>
       </c>
       <c r="M34" t="n">
-        <v>0.491139</v>
+        <v>0.453608</v>
       </c>
       <c r="N34" t="n">
         <v>0.2</v>
@@ -3756,7 +3748,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_15.txt</t>
+          <t>_2_15_1_1790731436_6.txt</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -3786,7 +3778,7 @@
         <v>0.1</v>
       </c>
       <c r="B35" t="n">
-        <v>0.249511</v>
+        <v>0.249519</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -3808,7 +3800,7 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>0.250172</v>
+        <v>0.250154</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="n">
@@ -3849,7 +3841,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_14.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_15.txt</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -3879,7 +3871,7 @@
         <v>0.1</v>
       </c>
       <c r="B36" t="n">
-        <v>0.249522</v>
+        <v>0.249491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -3901,7 +3893,7 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>0.250151</v>
+        <v>0.250196</v>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="n">
@@ -3942,7 +3934,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_0.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_11.txt</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -3972,7 +3964,7 @@
         <v>0.1</v>
       </c>
       <c r="B37" t="n">
-        <v>0.242237</v>
+        <v>0.242169</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -3989,25 +3981,25 @@
         <v>200000</v>
       </c>
       <c r="G37" t="n">
-        <v>0.549114</v>
+        <v>0.548336</v>
       </c>
       <c r="H37" t="n">
-        <v>0.445752</v>
+        <v>0.452288</v>
       </c>
       <c r="I37" t="n">
-        <v>0.492063</v>
+        <v>0.495702</v>
       </c>
       <c r="J37" t="n">
-        <v>0.258884</v>
+        <v>0.258467</v>
       </c>
       <c r="K37" t="n">
-        <v>0.477778</v>
+        <v>0.475676</v>
       </c>
       <c r="L37" t="n">
-        <v>0.436548</v>
+        <v>0.446701</v>
       </c>
       <c r="M37" t="n">
-        <v>0.456233</v>
+        <v>0.460733</v>
       </c>
       <c r="N37" t="n">
         <v>0.2</v>
@@ -4043,7 +4035,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_13.txt</t>
+          <t>_2_15_1_1790731436_7.txt</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -4073,7 +4065,7 @@
         <v>0.1</v>
       </c>
       <c r="B38" t="n">
-        <v>0.242124</v>
+        <v>0.24212</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4090,25 +4082,25 @@
         <v>200000</v>
       </c>
       <c r="G38" t="n">
-        <v>0.554098</v>
+        <v>0.535456</v>
       </c>
       <c r="H38" t="n">
-        <v>0.44183</v>
+        <v>0.48366</v>
       </c>
       <c r="I38" t="n">
-        <v>0.491636</v>
+        <v>0.508242</v>
       </c>
       <c r="J38" t="n">
-        <v>0.258685</v>
+        <v>0.258393</v>
       </c>
       <c r="K38" t="n">
-        <v>0.468927</v>
+        <v>0.466321</v>
       </c>
       <c r="L38" t="n">
-        <v>0.42132</v>
+        <v>0.456853</v>
       </c>
       <c r="M38" t="n">
-        <v>0.44385</v>
+        <v>0.461538</v>
       </c>
       <c r="N38" t="n">
         <v>0.2</v>
@@ -4144,7 +4136,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_9.txt</t>
+          <t>_2_15_1_1790731436_10.txt</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -4174,35 +4166,43 @@
         <v>0.1</v>
       </c>
       <c r="B39" t="n">
-        <v>0.249511</v>
+        <v>0.241918</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E39" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F39" t="n">
         <v>200000</v>
       </c>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="n">
+        <v>0.548105</v>
+      </c>
       <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>0.491503</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.518263</v>
+      </c>
       <c r="J39" t="n">
-        <v>0.250165</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
+        <v>0.258703</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.479592</v>
+      </c>
       <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="inlineStr"/>
+        <v>0.477157</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.478372</v>
+      </c>
       <c r="N39" t="n">
         <v>0.2</v>
       </c>
@@ -4237,23 +4237,23 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_18.txt</t>
+          <t>_2_15_1_1790731436_14.txt</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z39" t="n">
         <v>15</v>
       </c>
       <c r="AA39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4267,43 +4267,35 @@
         <v>0.1</v>
       </c>
       <c r="B40" t="n">
-        <v>0.241918</v>
+        <v>0.249522</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>_2_15_1_</t>
+          <t>_2_3_3_3_3_3_1_</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1790731436</v>
+        <v>1790731493</v>
       </c>
       <c r="E40" t="n">
-        <v>57</v>
+        <v>215</v>
       </c>
       <c r="F40" t="n">
         <v>200000</v>
       </c>
-      <c r="G40" t="n">
-        <v>0.548105</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>0.491503</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.518263</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="n">
-        <v>0.258703</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0.479592</v>
-      </c>
+        <v>0.25015</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="n">
-        <v>0.477157</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.478372</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>0.2</v>
       </c>
@@ -4338,23 +4330,23 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>_2_15_1_1790731436_14.txt</t>
+          <t>_2_3_3_3_3_3_1_1790731493_4.txt</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>[15]</t>
+          <t>[3, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="Z40" t="n">
         <v>15</v>
       </c>
       <c r="AA40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Angosta</t>
+          <t>Profunda</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4368,35 +4360,43 @@
         <v>0.1</v>
       </c>
       <c r="B41" t="n">
-        <v>0.249519</v>
+        <v>0.241885</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_</t>
+          <t>_2_15_1_</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1790731493</v>
+        <v>1790731436</v>
       </c>
       <c r="E41" t="n">
-        <v>215</v>
+        <v>57</v>
       </c>
       <c r="F41" t="n">
         <v>200000</v>
       </c>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>0.556426</v>
+      </c>
       <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>0.464052</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.506058</v>
+      </c>
       <c r="J41" t="n">
-        <v>0.250154</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
+        <v>0.259202</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.484043</v>
+      </c>
       <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="inlineStr"/>
+        <v>0.461929</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.472727</v>
+      </c>
       <c r="N41" t="n">
         <v>0.2</v>
       </c>
@@ -4431,23 +4431,23 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>_2_3_3_3_3_3_1_1790731493_15.txt</t>
+          <t>_2_15_1_1790731436_17.txt</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>[3, 3, 3, 3, 3]</t>
+          <t>[15]</t>
         </is>
       </c>
       <c r="Z41" t="n">
         <v>15</v>
       </c>
       <c r="AA41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Profunda</t>
+          <t>Angosta</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
@@ -4522,7 +4522,7 @@
         <v>0.468127</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0145088410360899</v>
+        <v>0.01450884103608991</v>
       </c>
       <c r="D2" t="n">
         <v>0.496203</v>
